--- a/farmacias.xlsx
+++ b/farmacias.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/germanbegani/Library/Mobile Documents/com~apple~CloudDocs/0 Alef /0 Molteni - Dolor/web_dolor/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B12AA3B0-54B6-9B42-A491-2871DA1FB9A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F45533-CD43-684F-9ECA-54E5C476936A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2420" yWindow="-19280" windowWidth="28760" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="217">
   <si>
     <t>name</t>
   </si>
@@ -441,9 +441,6 @@
     <t>(266) 442-0907</t>
   </si>
   <si>
-    <t>Farmacia Zentner</t>
-  </si>
-  <si>
     <t>San Jeronimo 3101</t>
   </si>
   <si>
@@ -585,9 +582,6 @@
     <t>Av. Belgrano 1194</t>
   </si>
   <si>
-    <t>Farmacia Chester - 20% Descuento a Particulares</t>
-  </si>
-  <si>
     <t>Farmacia Azul  - 20% Descuento a Particulares</t>
   </si>
   <si>
@@ -676,6 +670,21 @@
   </si>
   <si>
     <t>(11) 2479-1770</t>
+  </si>
+  <si>
+    <t>Farmacia TKL Tekiel - 40% Descuento a Particulares</t>
+  </si>
+  <si>
+    <t>Av. Santa Fe 2399</t>
+  </si>
+  <si>
+    <t>(11) 4823-1551</t>
+  </si>
+  <si>
+    <t>Farmacia Zentner - 40% Descuento a Particulares</t>
+  </si>
+  <si>
+    <t>Farmacia Chester - 25% Descuento a Particulares</t>
   </si>
 </sst>
 </file>
@@ -822,10 +831,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaFarmacias" displayName="TablaFarmacias" ref="A1:J51">
-  <autoFilter ref="A1:J51" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaFarmacias" displayName="TablaFarmacias" ref="A1:J52">
+  <autoFilter ref="A1:J52" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J33">
-    <sortCondition ref="A15:A33"/>
+    <sortCondition ref="A16:A33"/>
   </sortState>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="name"/>
@@ -1128,7 +1137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="41.1640625" customWidth="1"/>
@@ -1176,7 +1185,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
@@ -1201,13 +1210,13 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
@@ -1219,20 +1228,20 @@
         <v>1124791770</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>212</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>213</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
@@ -1243,18 +1252,18 @@
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3">
-        <v>1153530030</v>
+        <v>1148231551</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>62</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
         <v>61</v>
@@ -1268,21 +1277,21 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3">
-        <v>1147873100</v>
+        <v>1153530030</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>184</v>
+        <v>76</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="D6" t="s">
         <v>12</v>
@@ -1293,21 +1302,21 @@
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3">
-        <v>1139854640</v>
+        <v>1147873100</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="B7" t="s">
-        <v>181</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
         <v>12</v>
@@ -1317,18 +1326,22 @@
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+      <c r="H7" s="3">
+        <v>1139854640</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>202</v>
+      </c>
+      <c r="B8" t="s">
         <v>180</v>
       </c>
-      <c r="B8" t="s">
-        <v>182</v>
-      </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
@@ -1343,13 +1356,13 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="B9" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="C9" t="s">
-        <v>200</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
         <v>12</v>
@@ -1367,10 +1380,10 @@
         <v>201</v>
       </c>
       <c r="B10" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C10" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
@@ -1385,13 +1398,13 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>199</v>
+      </c>
+      <c r="B11" t="s">
+        <v>200</v>
+      </c>
+      <c r="C11" t="s">
         <v>205</v>
-      </c>
-      <c r="B11" t="s">
-        <v>206</v>
-      </c>
-      <c r="C11" t="s">
-        <v>84</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
@@ -1406,13 +1419,13 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
         <v>12</v>
@@ -1420,24 +1433,20 @@
       <c r="E12" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="4"/>
+      <c r="F12" s="3"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="3">
-        <v>1148015544</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>80</v>
-      </c>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
         <v>12</v>
@@ -1445,21 +1454,21 @@
       <c r="E13" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="3"/>
+      <c r="F13" s="4"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="4">
-        <v>1143221001</v>
+      <c r="H13" s="3">
+        <v>1148015544</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C14" t="s">
         <v>70</v>
@@ -1473,71 +1482,71 @@
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="4">
-        <v>1143286544</v>
+        <v>1143221001</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="D15" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="3" t="s">
-        <v>35</v>
+      <c r="H15" s="4">
+        <v>1143286544</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="E16" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="3">
-        <v>1155547975</v>
+      <c r="H16" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="C17" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="D17" t="s">
         <v>12</v>
@@ -1545,14 +1554,10 @@
       <c r="E17" t="s">
         <v>12</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>23</v>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3">
+        <v>1155547975</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>24</v>
@@ -1560,13 +1565,13 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D18" t="s">
         <v>12</v>
@@ -1589,10 +1594,10 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>145</v>
+        <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="C19" t="s">
         <v>17</v>
@@ -1603,24 +1608,28 @@
       <c r="E19" t="s">
         <v>12</v>
       </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3">
-        <v>1149611441</v>
+      <c r="F19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>108</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>10</v>
+        <v>144</v>
       </c>
       <c r="B20" t="s">
-        <v>192</v>
+        <v>107</v>
       </c>
       <c r="C20" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D20" t="s">
         <v>12</v>
@@ -1630,94 +1639,94 @@
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
-      <c r="H20" s="3" t="s">
-        <v>13</v>
+      <c r="H20" s="3">
+        <v>1149611441</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>190</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D21" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>141</v>
+        <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>142</v>
+        <v>67</v>
       </c>
       <c r="C22" t="s">
-        <v>143</v>
+        <v>28</v>
       </c>
       <c r="D22" t="s">
-        <v>146</v>
+        <v>28</v>
       </c>
       <c r="E22" t="s">
         <v>29</v>
       </c>
-      <c r="F22" s="3">
-        <v>1144302999</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="B23" t="s">
-        <v>91</v>
+        <v>141</v>
       </c>
       <c r="C23" t="s">
-        <v>92</v>
+        <v>142</v>
       </c>
       <c r="D23" t="s">
-        <v>92</v>
+        <v>145</v>
       </c>
       <c r="E23" t="s">
         <v>29</v>
       </c>
       <c r="F23" s="3">
-        <v>2235406049</v>
+        <v>1144302999</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>93</v>
+        <v>143</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B24" t="s">
-        <v>159</v>
+        <v>91</v>
       </c>
       <c r="C24" t="s">
         <v>92</v>
@@ -1728,71 +1737,71 @@
       <c r="E24" t="s">
         <v>29</v>
       </c>
-      <c r="F24" s="4">
-        <v>2235449668</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>160</v>
+      <c r="F24" s="3">
+        <v>2235406049</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B25" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C25" t="s">
-        <v>157</v>
+        <v>92</v>
       </c>
       <c r="D25" t="s">
-        <v>157</v>
+        <v>92</v>
       </c>
       <c r="E25" t="s">
         <v>29</v>
       </c>
-      <c r="F25" s="3">
-        <v>2915718813</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>158</v>
+      <c r="F25" s="4">
+        <v>2235449668</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>159</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>94</v>
+        <v>154</v>
       </c>
       <c r="B26" t="s">
-        <v>95</v>
+        <v>155</v>
       </c>
       <c r="C26" t="s">
-        <v>96</v>
+        <v>156</v>
       </c>
       <c r="D26" t="s">
-        <v>96</v>
+        <v>156</v>
       </c>
       <c r="E26" t="s">
         <v>29</v>
       </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3">
-        <v>2214214133</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>103</v>
-      </c>
+      <c r="F26" s="3">
+        <v>2915718813</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B27" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C27" t="s">
         <v>96</v>
@@ -1806,18 +1815,18 @@
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3">
-        <v>2214213400</v>
+        <v>2214214133</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B28" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C28" t="s">
         <v>96</v>
@@ -1831,18 +1840,18 @@
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3">
-        <v>2214890991</v>
+        <v>2214213400</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B29" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C29" t="s">
         <v>96</v>
@@ -1856,39 +1865,35 @@
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3">
-        <v>2214392600</v>
+        <v>2214890991</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>185</v>
+        <v>101</v>
       </c>
       <c r="B30" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="C30" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="D30" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="E30" t="s">
-        <v>39</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>42</v>
+        <v>29</v>
+      </c>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3">
+        <v>2214392600</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>43</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
@@ -1896,10 +1901,10 @@
         <v>183</v>
       </c>
       <c r="B31" t="s">
-        <v>191</v>
+        <v>37</v>
       </c>
       <c r="C31" t="s">
-        <v>187</v>
+        <v>38</v>
       </c>
       <c r="D31" t="s">
         <v>38</v>
@@ -1907,71 +1912,75 @@
       <c r="E31" t="s">
         <v>39</v>
       </c>
-      <c r="F31" s="3">
-        <v>2614637400</v>
+      <c r="F31" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
+        <v>41</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
+        <v>216</v>
+      </c>
+      <c r="B32" t="s">
         <v>189</v>
       </c>
-      <c r="B32" t="s">
-        <v>190</v>
-      </c>
       <c r="C32" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="D32" t="s">
-        <v>194</v>
+        <v>38</v>
       </c>
       <c r="E32" t="s">
         <v>39</v>
       </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="4">
-        <v>2622425585</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>195</v>
-      </c>
+      <c r="F32" s="3">
+        <v>2614637400</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>44</v>
+        <v>187</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>188</v>
       </c>
       <c r="C33" t="s">
-        <v>46</v>
+        <v>191</v>
       </c>
       <c r="D33" t="s">
-        <v>46</v>
+        <v>192</v>
       </c>
       <c r="E33" t="s">
-        <v>47</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="4">
+        <v>2622425585</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B34" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1985,18 +1994,18 @@
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>178</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B35" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C35" t="s">
         <v>46</v>
@@ -2010,18 +2019,18 @@
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="I35" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B36" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C36" t="s">
         <v>46</v>
@@ -2035,43 +2044,43 @@
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
       <c r="H36" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="I36" s="6" t="s">
         <v>172</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>135</v>
+        <v>44</v>
       </c>
       <c r="B37" t="s">
-        <v>136</v>
+        <v>45</v>
       </c>
       <c r="C37" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D37" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E37" t="s">
         <v>47</v>
       </c>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="3">
-        <v>3425912681</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>137</v>
-      </c>
+      <c r="F37" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>168</v>
+        <v>215</v>
       </c>
       <c r="B38" t="s">
-        <v>169</v>
+        <v>135</v>
       </c>
       <c r="C38" t="s">
         <v>47</v>
@@ -2082,76 +2091,75 @@
       <c r="E38" t="s">
         <v>47</v>
       </c>
-      <c r="F38" s="4">
-        <v>3425256633</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3">
+        <v>3425912681</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>85</v>
+        <v>167</v>
       </c>
       <c r="B39" t="s">
-        <v>86</v>
+        <v>168</v>
       </c>
       <c r="C39" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="D39" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="E39" t="s">
-        <v>88</v>
-      </c>
-      <c r="F39" s="5">
-        <v>2901584008</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="H39" s="3">
-        <v>2901425045</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>90</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="F39" s="4">
+        <v>3425256633</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="B40" t="s">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="C40" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="D40" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="E40" t="s">
-        <v>111</v>
-      </c>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="4">
-        <v>3814222879</v>
-      </c>
-      <c r="I40" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="J40" s="3"/>
+        <v>88</v>
+      </c>
+      <c r="F40" s="5">
+        <v>2901584008</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H40" s="3">
+        <v>2901425045</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>208</v>
+        <v>109</v>
       </c>
       <c r="B41" t="s">
-        <v>209</v>
+        <v>112</v>
       </c>
       <c r="C41" t="s">
         <v>110</v>
@@ -2165,47 +2173,48 @@
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
       <c r="H41" s="4">
-        <v>3814237198</v>
-      </c>
-      <c r="I41" s="4" t="s">
-        <v>210</v>
+        <v>3814222879</v>
+      </c>
+      <c r="I41" s="9" t="s">
+        <v>113</v>
       </c>
       <c r="J41" s="3"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>118</v>
+        <v>206</v>
       </c>
       <c r="B42" t="s">
-        <v>114</v>
+        <v>207</v>
       </c>
       <c r="C42" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="D42" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E42" t="s">
-        <v>115</v>
-      </c>
-      <c r="F42" s="3">
-        <v>3516020243</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
+        <v>111</v>
+      </c>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="4">
+        <v>3814237198</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="J42" s="3"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B43" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C43" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="D43" t="s">
         <v>115</v>
@@ -2224,13 +2233,13 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B44" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C44" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D44" t="s">
         <v>115</v>
@@ -2249,13 +2258,13 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B45" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C45" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="D45" t="s">
         <v>115</v>
@@ -2264,20 +2273,20 @@
         <v>115</v>
       </c>
       <c r="F45" s="3">
-        <v>3518173000</v>
+        <v>3516020243</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B46" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C46" t="s">
         <v>139</v>
@@ -2299,10 +2308,10 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B47" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C47" t="s">
         <v>138</v>
@@ -2324,128 +2333,153 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="B48" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="C48" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="D48" t="s">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="E48" t="s">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="F48" s="3">
-        <v>3794725782</v>
+        <v>3518173000</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B49" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C49" t="s">
+        <v>148</v>
+      </c>
+      <c r="D49" t="s">
         <v>149</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
+        <v>149</v>
+      </c>
+      <c r="F49" s="3">
+        <v>3794725782</v>
+      </c>
+      <c r="G49" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="E49" t="s">
-        <v>150</v>
-      </c>
-      <c r="F49" s="3">
-        <v>3794886003</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>154</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="B50" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="C50" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="D50" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="E50" t="s">
-        <v>133</v>
-      </c>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
-      <c r="H50" s="3">
-        <v>2664420907</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>134</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="F50" s="3">
+        <v>3794886003</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H50" s="3"/>
+      <c r="I50" s="3"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
+        <v>131</v>
+      </c>
+      <c r="B51" t="s">
+        <v>132</v>
+      </c>
+      <c r="C51" t="s">
+        <v>133</v>
+      </c>
+      <c r="D51" t="s">
+        <v>133</v>
+      </c>
+      <c r="E51" t="s">
+        <v>133</v>
+      </c>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3">
+        <v>2664420907</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>162</v>
+      </c>
+      <c r="B52" t="s">
         <v>163</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C52" t="s">
         <v>164</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D52" t="s">
+        <v>164</v>
+      </c>
+      <c r="E52" t="s">
         <v>165</v>
       </c>
-      <c r="D51" t="s">
-        <v>165</v>
-      </c>
-      <c r="E51" t="s">
+      <c r="F52" s="7">
+        <v>3625628866</v>
+      </c>
+      <c r="G52" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="F51" s="7">
-        <v>3625628866</v>
-      </c>
-      <c r="G51" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="H51" s="3">
+      <c r="H52" s="3">
         <v>3625427244</v>
       </c>
-      <c r="I51" s="8" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="F52" s="3"/>
-      <c r="G52" s="3"/>
+      <c r="I52" s="8" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H13" r:id="rId1" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+rp+went&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{5466422A-0693-4945-A541-40C2AFE25C02}"/>
-    <hyperlink ref="H14" r:id="rId2" display="https://www.google.com/search?q=farmacia+rp+viamonte&amp;client=safari&amp;hs=Xtj9&amp;sca_esv=207ca25c77663f86&amp;rls=en&amp;sxsrf=AE3TifM4DZ0u4Ubf3LGwkNHa6GDtQ1Y8sw%3A1767101236673&amp;ei=NNNTabjxKPjU5OUPtNewyAw&amp;ved=0ahUKEwi42_mLteWRAxV4KrkGHbQrDMkQ4dUDCBE&amp;uact=5&amp;oq=farmacia+rp+viamonte&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiFGZhcm1hY2lhIHJwIHZpYW1vbnRlMgsQLhiABBjHARivATIFEAAYgAQyBhAAGBYYHjICECYyCBAAGIAEGKIEMhoQLhiABBjHARivARiXBRjcBBjeBBjgBNgBAUjTDVC9BVicDHABeAGQAQCYAbgBoAH6B6oBAzIuNrgBA8gBAPgBAZgCCaACtwjCAgcQIxiwAxgnwgIKEAAYRxjWBBiwA8ICExAuGIAEGIoFGEMYxwEY0QMYsAOYAwCIBgGQBgq6BgYIARABGBSSBwMzLjagB9lAsgcDMi42uAexCMIHBTItOC4xyActgAgB&amp;sclient=gws-wiz-serp" xr:uid="{C0BD8BFB-29E1-644A-BB2C-960C8D742171}"/>
-    <hyperlink ref="H40" r:id="rId3" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{29ABEFDF-32B0-3A49-BB75-2B6D5BEB8B04}"/>
-    <hyperlink ref="I40" r:id="rId4" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{D063495B-8203-214D-A909-FA46D4D33C38}"/>
-    <hyperlink ref="F24" r:id="rId5" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+previley&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{F37501A8-48B0-9D45-80CD-40426B4DD134}"/>
-    <hyperlink ref="G24" r:id="rId6" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+previley&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{378344CB-6A0A-264B-A0DF-7ADA57385A21}"/>
-    <hyperlink ref="F38" r:id="rId7" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+azanza+santa+fe&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{CFFBF7EB-54C2-2C4A-B013-12559FBCDDDF}"/>
-    <hyperlink ref="G38" r:id="rId8" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+azanza+santa+fe&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{18DD9A59-F031-C443-9980-4C77ECA89901}"/>
+    <hyperlink ref="H14" r:id="rId1" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+rp+went&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{5466422A-0693-4945-A541-40C2AFE25C02}"/>
+    <hyperlink ref="H15" r:id="rId2" display="https://www.google.com/search?q=farmacia+rp+viamonte&amp;client=safari&amp;hs=Xtj9&amp;sca_esv=207ca25c77663f86&amp;rls=en&amp;sxsrf=AE3TifM4DZ0u4Ubf3LGwkNHa6GDtQ1Y8sw%3A1767101236673&amp;ei=NNNTabjxKPjU5OUPtNewyAw&amp;ved=0ahUKEwi42_mLteWRAxV4KrkGHbQrDMkQ4dUDCBE&amp;uact=5&amp;oq=farmacia+rp+viamonte&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiFGZhcm1hY2lhIHJwIHZpYW1vbnRlMgsQLhiABBjHARivATIFEAAYgAQyBhAAGBYYHjICECYyCBAAGIAEGKIEMhoQLhiABBjHARivARiXBRjcBBjeBBjgBNgBAUjTDVC9BVicDHABeAGQAQCYAbgBoAH6B6oBAzIuNrgBA8gBAPgBAZgCCaACtwjCAgcQIxiwAxgnwgIKEAAYRxjWBBiwA8ICExAuGIAEGIoFGEMYxwEY0QMYsAOYAwCIBgGQBgq6BgYIARABGBSSBwMzLjagB9lAsgcDMi42uAexCMIHBTItOC4xyActgAgB&amp;sclient=gws-wiz-serp" xr:uid="{C0BD8BFB-29E1-644A-BB2C-960C8D742171}"/>
+    <hyperlink ref="H41" r:id="rId3" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{29ABEFDF-32B0-3A49-BB75-2B6D5BEB8B04}"/>
+    <hyperlink ref="I41" r:id="rId4" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmarket&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{D063495B-8203-214D-A909-FA46D4D33C38}"/>
+    <hyperlink ref="F25" r:id="rId5" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+previley&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{F37501A8-48B0-9D45-80CD-40426B4DD134}"/>
+    <hyperlink ref="G25" r:id="rId6" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+previley&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{378344CB-6A0A-264B-A0DF-7ADA57385A21}"/>
+    <hyperlink ref="F39" r:id="rId7" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+azanza+santa+fe&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{CFFBF7EB-54C2-2C4A-B013-12559FBCDDDF}"/>
+    <hyperlink ref="G39" r:id="rId8" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+azanza+santa+fe&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{18DD9A59-F031-C443-9980-4C77ECA89901}"/>
     <hyperlink ref="H36" r:id="rId9" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+cubo+rosario&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{75185B76-E4CA-B045-94FF-09A4E362959D}"/>
     <hyperlink ref="I36" r:id="rId10" display="https://www.google.com/search?client=safari&amp;rls=en&amp;q=farmacia+cubo+rosario&amp;ie=UTF-8&amp;oe=UTF-8" xr:uid="{87B00BF1-A473-B148-9C6C-8E948C5E80B8}"/>
     <hyperlink ref="H35" r:id="rId11" display="https://www.google.com/search?q=farmacia+lagos+rosario&amp;client=safari&amp;hs=UWnp&amp;sca_esv=73844655aaedfbf5&amp;rls=en&amp;sxsrf=ANbL-n6KeCqa0win5PaQWVs7MLCl1D7-Yg%3A1777471052678&amp;ei=TA7yaef4KL7W1sQPxb7OoAw&amp;biw=1470&amp;bih=757&amp;ved=0ahUKEwjnzsXVm5OUAxU-q5UCHUWfE8QQ4dUDCBE&amp;uact=5&amp;oq=farmacia+lagos+rosario&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiFmZhcm1hY2lhIGxhZ29zIHJvc2FyaW8yBhAAGAgYHjIGEAAYCBgeMgYQABgIGB4yBhAAGAgYHjIIEAAYgAQYogQyBRAAGO8FMggQABiABBiiBDIIEAAYgAQYogQyBRAAGO8FSKkPULMEWJ0JcAF4AJABAJgBeKAB5AOqAQMzLjK4AQPIAQD4AQGYAgWgApkDwgIIEAAYgAQYsAPCAgsQABiABBiiBBiwA8ICCBAAGO8FGLADwgIGEAAYBxgewgIIEAAYCBgHGB6YAwCIBgGQBgWSBwM0LjGgB8YhsgcDMy4xuAePA8IHBTItMy4yyAcdgAgB&amp;sclient=gws-wiz-serp" xr:uid="{02453522-7934-C14C-9FA8-D4262EDA011E}"/>
     <hyperlink ref="I35" r:id="rId12" display="https://www.google.com/search?q=farmacia+lagos+rosario&amp;client=safari&amp;hs=UWnp&amp;sca_esv=73844655aaedfbf5&amp;rls=en&amp;sxsrf=ANbL-n6KeCqa0win5PaQWVs7MLCl1D7-Yg%3A1777471052678&amp;ei=TA7yaef4KL7W1sQPxb7OoAw&amp;biw=1470&amp;bih=757&amp;ved=0ahUKEwjnzsXVm5OUAxU-q5UCHUWfE8QQ4dUDCBE&amp;uact=5&amp;oq=farmacia+lagos+rosario&amp;gs_lp=Egxnd3Mtd2l6LXNlcnAiFmZhcm1hY2lhIGxhZ29zIHJvc2FyaW8yBhAAGAgYHjIGEAAYCBgeMgYQABgIGB4yBhAAGAgYHjIIEAAYgAQYogQyBRAAGO8FMggQABiABBiiBDIIEAAYgAQYogQyBRAAGO8FSKkPULMEWJ0JcAF4AJABAJgBeKAB5AOqAQMzLjK4AQPIAQD4AQGYAgWgApkDwgIIEAAYgAQYsAPCAgsQABiABBiiBBiwA8ICCBAAGO8FGLADwgIGEAAYBxgewgIIEAAYCBgHGB6YAwCIBgGQBgWSBwM0LjGgB8YhsgcDMy4xuAePA8IHBTItMy4yyAcdgAgB&amp;sclient=gws-wiz-serp" xr:uid="{9AF63C30-9BA4-8045-B2AC-97A6AEC324D6}"/>
-    <hyperlink ref="H32" r:id="rId13" display="tel:(02622) 42-5585" xr:uid="{3BBF1536-921E-6741-9023-473CF19052A5}"/>
-    <hyperlink ref="I32" r:id="rId14" display="tel:(02622) 42-5585" xr:uid="{0B4D10C9-136D-4C4F-9997-41F7B999118F}"/>
+    <hyperlink ref="H33" r:id="rId13" display="tel:(02622) 42-5585" xr:uid="{3BBF1536-921E-6741-9023-473CF19052A5}"/>
+    <hyperlink ref="I33" r:id="rId14" display="tel:(02622) 42-5585" xr:uid="{0B4D10C9-136D-4C4F-9997-41F7B999118F}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/farmacias.xlsx
+++ b/farmacias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/germanbegani/Library/Mobile Documents/com~apple~CloudDocs/0 Alef /0 Molteni - Dolor/web_dolor/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F45533-CD43-684F-9ECA-54E5C476936A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0477D3DC-717C-864D-B23E-2CEFACC89ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2420" yWindow="-19280" windowWidth="28760" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5260" yWindow="-19820" windowWidth="28760" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Farmacias" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="221">
   <si>
     <t>name</t>
   </si>
@@ -438,9 +438,6 @@
     <t>San Luis</t>
   </si>
   <si>
-    <t>(266) 442-0907</t>
-  </si>
-  <si>
     <t>San Jeronimo 3101</t>
   </si>
   <si>
@@ -685,6 +682,21 @@
   </si>
   <si>
     <t>Farmacia Chester - 25% Descuento a Particulares</t>
+  </si>
+  <si>
+    <t>Farmacia Molina</t>
+  </si>
+  <si>
+    <t>Poeta Agüero 323</t>
+  </si>
+  <si>
+    <t>Merlo</t>
+  </si>
+  <si>
+    <t>(2656) 47-0674</t>
+  </si>
+  <si>
+    <t>(2664) 42-0907</t>
   </si>
 </sst>
 </file>
@@ -831,8 +843,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaFarmacias" displayName="TablaFarmacias" ref="A1:J52">
-  <autoFilter ref="A1:J52" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaFarmacias" displayName="TablaFarmacias" ref="A1:J53">
+  <autoFilter ref="A1:J53" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J33">
     <sortCondition ref="A16:A33"/>
   </sortState>
@@ -1137,7 +1149,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="41.1640625" customWidth="1"/>
@@ -1185,7 +1197,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
@@ -1210,13 +1222,13 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C3" t="s">
         <v>209</v>
-      </c>
-      <c r="C3" t="s">
-        <v>210</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
@@ -1228,17 +1240,17 @@
         <v>1124791770</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B4" t="s">
         <v>212</v>
-      </c>
-      <c r="B4" t="s">
-        <v>213</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
@@ -1255,7 +1267,7 @@
         <v>1148231551</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -1310,7 +1322,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B7" t="s">
         <v>82</v>
@@ -1335,10 +1347,10 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C8" t="s">
         <v>65</v>
@@ -1356,10 +1368,10 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C9" t="s">
         <v>84</v>
@@ -1377,13 +1389,13 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B10" t="s">
+        <v>196</v>
+      </c>
+      <c r="C10" t="s">
         <v>197</v>
-      </c>
-      <c r="C10" t="s">
-        <v>198</v>
       </c>
       <c r="D10" t="s">
         <v>12</v>
@@ -1398,13 +1410,13 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B11" t="s">
         <v>199</v>
       </c>
-      <c r="B11" t="s">
-        <v>200</v>
-      </c>
       <c r="C11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
@@ -1419,10 +1431,10 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>202</v>
+      </c>
+      <c r="B12" t="s">
         <v>203</v>
-      </c>
-      <c r="B12" t="s">
-        <v>204</v>
       </c>
       <c r="C12" t="s">
         <v>84</v>
@@ -1623,7 +1635,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B20" t="s">
         <v>107</v>
@@ -1651,7 +1663,7 @@
         <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C21" t="s">
         <v>11</v>
@@ -1698,16 +1710,16 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>139</v>
+      </c>
+      <c r="B23" t="s">
         <v>140</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>141</v>
       </c>
-      <c r="C23" t="s">
-        <v>142</v>
-      </c>
       <c r="D23" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E23" t="s">
         <v>29</v>
@@ -1716,14 +1728,14 @@
         <v>1144302999</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B24" t="s">
         <v>91</v>
@@ -1748,10 +1760,10 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B25" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C25" t="s">
         <v>92</v>
@@ -1766,23 +1778,23 @@
         <v>2235449668</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>153</v>
+      </c>
+      <c r="B26" t="s">
         <v>154</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>155</v>
       </c>
-      <c r="C26" t="s">
-        <v>156</v>
-      </c>
       <c r="D26" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E26" t="s">
         <v>29</v>
@@ -1791,7 +1803,7 @@
         <v>2915718813</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
@@ -1898,7 +1910,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B31" t="s">
         <v>37</v>
@@ -1927,13 +1939,13 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B32" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C32" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D32" t="s">
         <v>38</v>
@@ -1945,23 +1957,23 @@
         <v>2614637400</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
+        <v>186</v>
+      </c>
+      <c r="B33" t="s">
         <v>187</v>
       </c>
-      <c r="B33" t="s">
-        <v>188</v>
-      </c>
       <c r="C33" t="s">
+        <v>190</v>
+      </c>
+      <c r="D33" t="s">
         <v>191</v>
-      </c>
-      <c r="D33" t="s">
-        <v>192</v>
       </c>
       <c r="E33" t="s">
         <v>39</v>
@@ -1972,15 +1984,15 @@
         <v>2622425585</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B34" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C34" t="s">
         <v>46</v>
@@ -1994,18 +2006,18 @@
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>177</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B35" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C35" t="s">
         <v>46</v>
@@ -2019,18 +2031,18 @@
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="I35" s="6" t="s">
         <v>174</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B36" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C36" t="s">
         <v>46</v>
@@ -2044,10 +2056,10 @@
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
       <c r="H36" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="I36" s="6" t="s">
         <v>171</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
@@ -2077,10 +2089,10 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B38" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C38" t="s">
         <v>47</v>
@@ -2097,15 +2109,15 @@
         <v>3425912681</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
+        <v>166</v>
+      </c>
+      <c r="B39" t="s">
         <v>167</v>
-      </c>
-      <c r="B39" t="s">
-        <v>168</v>
       </c>
       <c r="C39" t="s">
         <v>47</v>
@@ -2120,7 +2132,7 @@
         <v>3425256633</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
@@ -2182,10 +2194,10 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
+        <v>205</v>
+      </c>
+      <c r="B42" t="s">
         <v>206</v>
-      </c>
-      <c r="B42" t="s">
-        <v>207</v>
       </c>
       <c r="C42" t="s">
         <v>110</v>
@@ -2202,7 +2214,7 @@
         <v>3814237198</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J42" s="3"/>
     </row>
@@ -2214,7 +2226,7 @@
         <v>114</v>
       </c>
       <c r="C43" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D43" t="s">
         <v>115</v>
@@ -2289,7 +2301,7 @@
         <v>124</v>
       </c>
       <c r="C46" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D46" t="s">
         <v>115</v>
@@ -2314,7 +2326,7 @@
         <v>127</v>
       </c>
       <c r="C47" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D47" t="s">
         <v>115</v>
@@ -2339,7 +2351,7 @@
         <v>129</v>
       </c>
       <c r="C48" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D48" t="s">
         <v>115</v>
@@ -2358,50 +2370,50 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
+        <v>145</v>
+      </c>
+      <c r="B49" t="s">
         <v>146</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>147</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>148</v>
       </c>
-      <c r="D49" t="s">
-        <v>149</v>
-      </c>
       <c r="E49" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F49" s="3">
         <v>3794725782</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
+        <v>150</v>
+      </c>
+      <c r="B50" t="s">
         <v>151</v>
       </c>
-      <c r="B50" t="s">
-        <v>152</v>
-      </c>
       <c r="C50" t="s">
+        <v>147</v>
+      </c>
+      <c r="D50" t="s">
         <v>148</v>
       </c>
-      <c r="D50" t="s">
-        <v>149</v>
-      </c>
       <c r="E50" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F50" s="3">
         <v>3794886003</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
@@ -2428,41 +2440,66 @@
         <v>2664420907</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>134</v>
+        <v>220</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
+        <v>216</v>
+      </c>
+      <c r="B52" t="s">
+        <v>217</v>
+      </c>
+      <c r="C52" t="s">
+        <v>218</v>
+      </c>
+      <c r="D52" t="s">
+        <v>133</v>
+      </c>
+      <c r="E52" t="s">
+        <v>133</v>
+      </c>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+      <c r="H52" s="3">
+        <v>2656470674</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>161</v>
+      </c>
+      <c r="B53" t="s">
         <v>162</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C53" t="s">
         <v>163</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D53" t="s">
+        <v>163</v>
+      </c>
+      <c r="E53" t="s">
         <v>164</v>
       </c>
-      <c r="D52" t="s">
-        <v>164</v>
-      </c>
-      <c r="E52" t="s">
+      <c r="F53" s="7">
+        <v>3625628866</v>
+      </c>
+      <c r="G53" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="F52" s="7">
-        <v>3625628866</v>
-      </c>
-      <c r="G52" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="H53" s="3">
         <v>3625427244</v>
       </c>
-      <c r="I52" s="8" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="F53" s="3"/>
-      <c r="G53" s="3"/>
+      <c r="I53" s="8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
